--- a/reports/pdf_rolling5_20260713.xlsx
+++ b/reports/pdf_rolling5_20260713.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-07-06 ~ 2026-07-13  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-07-06 ~ 2026-07-13  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -751,18 +751,18 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>파두  (신규)</t>
+          <t>원익머트리얼즈  (신규)</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>66</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>5134694400</v>
+        <v>2517203700</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.05%</t>
+          <t>0.00%→0.52%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -795,18 +795,18 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈  (신규)</t>
+          <t>파두  (신규)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>66</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2517203700</v>
+        <v>5134694400</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.52%</t>
+          <t>0.00%→1.05%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -992,23 +992,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>RFHIC</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-17</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-536434150</v>
+        <v>-897214100</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>0.88%→0.63%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>32→15</t>
+          <t>75→58</t>
         </is>
       </c>
     </row>
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>RFHIC</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-17</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-897214100</v>
+        <v>-536434150</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.88%→0.63%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>75→58</t>
+          <t>32→15</t>
         </is>
       </c>
     </row>
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1618267500</v>
+        <v>1641060000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.69%→2.93%</t>
+          <t>3.60%→3.84%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G21" s="17" t="n"/>
@@ -1351,23 +1351,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>421914500</v>
+        <v>1618267500</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.65%→2.96%</t>
+          <t>2.69%→2.93%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G22" s="17" t="n"/>
@@ -1379,23 +1379,23 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1641060000</v>
+        <v>421914500</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>3.60%→3.84%</t>
+          <t>2.65%→2.96%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>166→171</t>
         </is>
       </c>
       <c r="G23" s="17" t="n"/>
@@ -1429,829 +1429,1115 @@
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="20" t="n"/>
-      <c r="H28" s="20" t="n"/>
-      <c r="I28" s="20" t="n"/>
-      <c r="J28" s="20" t="n"/>
-      <c r="K28" s="20" t="n"/>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="n"/>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="20" t="n"/>
-      <c r="G30" s="20" t="n"/>
-      <c r="H30" s="20" t="n"/>
-      <c r="I30" s="20" t="n"/>
-      <c r="J30" s="20" t="n"/>
-      <c r="K30" s="20" t="n"/>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,562억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 4종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>201</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>6213915000</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>6.59%→8.29%</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>549→750</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>-86</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>-7385250000</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>4.81%→2.15%</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>156→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>엘앤씨바이오  (신규)</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>6942341100</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.48%</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>0→139</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>-81</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>-4958147700</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>3.18%→1.51%</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>150→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>파마리서치  (신규)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>7682377500</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.75%</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>0→35</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-66</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>-8057273400</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>9.69%→7.42%</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>236→170</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>1404983700</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>1.30%→1.74%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>42→59</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>하나마이크론</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-58</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-1583878500</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>2.37%→1.87%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>249→191</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>-4520460000</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>3.87%→2.42%</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>100→60</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,548억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 329억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 15종목  /  매도 14종목</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K42" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="n">
-        <v>209</v>
-      </c>
-      <c r="C35" s="11" t="n">
-        <v>151713100</v>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>6.72%→7.17%</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>3,020→3,229</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H35" s="15" t="n">
-        <v>-318</v>
-      </c>
-      <c r="I35" s="15" t="n">
-        <v>-100551600</v>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
-        <is>
-          <t>2.96%→2.65%</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="inlineStr">
-        <is>
-          <t>3,054→2,736</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>에이프로</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="n">
-        <v>91</v>
-      </c>
-      <c r="C36" s="11" t="n">
-        <v>21541975</v>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>0.37%→0.44%</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>510→601</t>
-        </is>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>LS증권</t>
-        </is>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>-101</v>
-      </c>
-      <c r="I36" s="15" t="n">
-        <v>-55544950</v>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>0.48%→0.31%</t>
-        </is>
-      </c>
-      <c r="K36" s="13" t="inlineStr">
-        <is>
-          <t>285→184</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="C37" s="11" t="n">
-        <v>177174000</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>1.87%→2.41%</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>186→240</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>-36</v>
-      </c>
-      <c r="I37" s="15" t="n">
-        <v>-99450000</v>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>6.21%→5.89%</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="inlineStr">
-        <is>
-          <t>733→697</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>네패스아크</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C38" s="11" t="n">
-        <v>47396000</v>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>0.19%→0.34%</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>21→37</t>
-        </is>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>서부T&amp;D</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>-36</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>-31518000</v>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>0.20%→0.10%</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>73→37</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>알멕</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>32831250</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>0.56%→0.66%</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>83→98</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>더핑크퐁컴퍼니</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>-31501000</v>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>0.23%→0.14%</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>82→48</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>106998000</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>2.32%→2.65%</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>85→97</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>채비  (편출)</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>-16010600</v>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>0.05%→0.00%</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>34→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>코미코</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C41" s="11" t="n">
-        <v>64515000</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>2.81%→3.00%</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>142→152</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>다우데이타</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>-31</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>-46165200</v>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>0.34%→0.20%</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>75→44</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>HPSP</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>33405000</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>1.17%→1.27%</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>114→124</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>삼현  (편출)</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>-27</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>-77571000</v>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>0.24%→0.00%</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>27→0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
-        <v>9</v>
+        <v>209</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>17671500</v>
+        <v>151713100</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>2.71%→2.76%</t>
+          <t>6.72%→7.17%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>451→460</t>
+          <t>3,020→3,229</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-14</v>
+        <v>-318</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-40162500</v>
+        <v>-100551600</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.61%</t>
+          <t>2.96%→2.65%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>3,054→2,736</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>에이프로</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>38046000</v>
+        <v>21541975</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>1.42%→1.53%</t>
+          <t>0.37%→0.44%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>510→601</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>LS증권</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-14</v>
+        <v>-101</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-35759500</v>
+        <v>-55544950</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.10%</t>
+          <t>0.48%→0.31%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>285→184</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>36618000</v>
+        <v>177174000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>0.92%→1.03%</t>
+          <t>1.87%→2.41%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>49→55</t>
+          <t>186→240</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-10</v>
+        <v>-36</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-73610000</v>
+        <v>-99450000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>1.08%→0.86%</t>
+          <t>6.21%→5.89%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>48→38</t>
+          <t>733→697</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>38709000</v>
+        <v>47396000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>0.91%→1.03%</t>
+          <t>0.19%→0.34%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>46→52</t>
+          <t>21→37</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-7</v>
+        <v>-36</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-68544000</v>
+        <v>-31518000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>3.21%→2.99%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>107→100</t>
+          <t>73→37</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>코스메카코리아  (신규)</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>36337500</v>
+        <v>32831250</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.11%</t>
+          <t>0.56%→0.66%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>0→5</t>
+          <t>83→98</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-6</v>
+        <v>-34</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-18130500</v>
+        <v>-31501000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.73%</t>
+          <t>0.23%→0.14%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>85→79</t>
+          <t>82→48</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>17722500</v>
+        <v>106998000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>6.83%→6.87%</t>
+          <t>2.32%→2.65%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>629→634</t>
+          <t>85→97</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>채비  (편출)</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-3</v>
+        <v>-34</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-73567500</v>
+        <v>-16010600</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>2.03%→1.80%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>27→24</t>
+          <t>34→0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>64515000</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>2.81%→3.00%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>142→152</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>다우데이타</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-31</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-46165200</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>0.34%→0.20%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>75→44</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>33405000</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>1.17%→1.27%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>114→124</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>삼현  (편출)</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-77571000</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>0.24%→0.00%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>27→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>17671500</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>2.71%→2.76%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>451→460</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>하이록코리아</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-35759500</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>0.21%→0.10%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>27→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>씨엠티엑스</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>38709000</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>0.91%→1.03%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>46→52</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-40162500</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>0.73%→0.61%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>83→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>36618000</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>0.92%→1.03%</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>49→55</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-73610000</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>1.08%→0.86%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>48→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>38046000</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>1.42%→1.53%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>73→79</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-68544000</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>3.21%→2.99%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>107→100</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>17722500</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>6.83%→6.87%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>629→634</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-18130500</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>0.79%→0.73%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>85→79</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>코스메카코리아  (신규)</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>36337500</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.11%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>0→5</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>파크시스템스</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-73567500</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>2.03%→1.80%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>27→24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
           <t>피에스케이</t>
         </is>
       </c>
-      <c r="B49" s="11" t="n">
+      <c r="B57" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C49" s="11" t="n">
+      <c r="C57" s="11" t="n">
         <v>51748000</v>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>2.50%→2.65%</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="E57" s="13" t="inlineStr">
         <is>
           <t>63→67</t>
         </is>
       </c>
-      <c r="G49" s="17" t="n"/>
-      <c r="H49" s="17" t="n"/>
-      <c r="I49" s="17" t="n"/>
-      <c r="J49" s="17" t="n"/>
-      <c r="K49" s="17" t="n"/>
-    </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="G57" s="17" t="n"/>
+      <c r="H57" s="17" t="n"/>
+      <c r="I57" s="17" t="n"/>
+      <c r="J57" s="17" t="n"/>
+      <c r="K57" s="17" t="n"/>
+    </row>
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 568억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="19" t="inlineStr">
+    <row r="62" ht="19" customHeight="1">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B54" s="20" t="n"/>
-      <c r="C54" s="20" t="n"/>
-      <c r="D54" s="20" t="n"/>
-      <c r="E54" s="20" t="n"/>
-      <c r="F54" s="20" t="n"/>
-      <c r="G54" s="20" t="n"/>
-      <c r="H54" s="20" t="n"/>
-      <c r="I54" s="20" t="n"/>
-      <c r="J54" s="20" t="n"/>
-      <c r="K54" s="20" t="n"/>
+      <c r="B62" s="20" t="n"/>
+      <c r="C62" s="20" t="n"/>
+      <c r="D62" s="20" t="n"/>
+      <c r="E62" s="20" t="n"/>
+      <c r="F62" s="20" t="n"/>
+      <c r="G62" s="20" t="n"/>
+      <c r="H62" s="20" t="n"/>
+      <c r="I62" s="20" t="n"/>
+      <c r="J62" s="20" t="n"/>
+      <c r="K62" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G29:K29"/>
+    <mergeCell ref="A62:K62"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="A59:K59"/>
     <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G33:K33"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A52:K52"/>
+    <mergeCell ref="G41:K41"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A60:K60"/>
+    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A37:K37"/>
     <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_rolling5_20260713.xlsx
+++ b/reports/pdf_rolling5_20260713.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,448억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 18종목  /  매도 15종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,826억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 18종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>164</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1584899280</v>
+        <v>1564560000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-54</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-938139300</v>
+        <v>-926100000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>93</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1016515110</v>
+        <v>1003470000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-52</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1754110800</v>
+        <v>-1731600000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -751,18 +751,18 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈  (신규)</t>
+          <t>파두  (신규)</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>66</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2517203700</v>
+        <v>5068800000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.52%</t>
+          <t>0.00%→1.05%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -779,7 +779,7 @@
         <v>-37</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1163785050</v>
+        <v>-1148850000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -795,18 +795,18 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>파두  (신규)</t>
+          <t>원익머트리얼즈  (신규)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>66</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>5134694400</v>
+        <v>2484900000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.05%</t>
+          <t>0.00%→0.52%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -823,7 +823,7 @@
         <v>-25</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-4500252500</v>
+        <v>-4442500000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>43</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>554070480</v>
+        <v>546960000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-23</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2912375000</v>
+        <v>-2875000000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>27</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2436974100</v>
+        <v>2405700000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-20</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-959311000</v>
+        <v>-947000000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1793313900</v>
+        <v>1770300000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-19</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1395407500</v>
+        <v>-1377500000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1158872000</v>
+        <v>1144000000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-17</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-897214100</v>
+        <v>-885700000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1447374400</v>
+        <v>1428800000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-17</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-536434150</v>
+        <v>-529550000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>485632200</v>
+        <v>479400000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-16</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-3069795200</v>
+        <v>-3030400000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>469677450</v>
+        <v>463650000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-483201000</v>
+        <v>-477000000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1147,23 +1147,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>477629500</v>
+        <v>422000000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.82%→1.84%</t>
+          <t>0.23%→0.32%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>27→37</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1175,7 +1175,7 @@
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-909268800</v>
+        <v>-897600000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>427486000</v>
+        <v>471500000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.23%→0.32%</t>
+          <t>1.82%→1.84%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>27→37</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1219,7 +1219,7 @@
         <v>-10</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-509539000</v>
+        <v>-503000000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>8</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>994360800</v>
+        <v>981600000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>-6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-999831000</v>
+        <v>-987000000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>7</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>965794200</v>
+        <v>953400000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>-4</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-487455600</v>
+        <v>-481200000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1641060000</v>
+        <v>1597500000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>3.60%→3.84%</t>
+          <t>2.69%→2.93%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G21" s="17" t="n"/>
@@ -1351,23 +1351,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1618267500</v>
+        <v>1620000000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.69%→2.93%</t>
+          <t>3.60%→3.84%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G22" s="17" t="n"/>
@@ -1386,7 +1386,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>421914500</v>
+        <v>416500000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,303억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,371억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1431,7 +1431,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,562억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,815억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1527,7 +1527,7 @@
         <v>201</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>6213915000</v>
+        <v>6204870000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>-86</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-7385250000</v>
+        <v>-7374500000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>139</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>6942341100</v>
+        <v>6932235800</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>-81</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-4958147700</v>
+        <v>-4950930600</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>35</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>7682377500</v>
+        <v>7671195000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>-66</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-8057273400</v>
+        <v>-8045545200</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>17</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1404983700</v>
+        <v>1402938600</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>-58</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1583878500</v>
+        <v>-1581573000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>-40</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-4520460000</v>
+        <v>-4513880000</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,548억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,598억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1748,7 +1748,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 329억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 15종목  /  매도 14종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 363억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 15종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1844,11 +1844,11 @@
         <v>209</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>151713100</v>
+        <v>158641450</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>6.72%→7.17%</t>
+          <t>6.38%→6.80%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1865,11 +1865,11 @@
         <v>-318</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-100551600</v>
+        <v>-107444250</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>2.96%→2.65%</t>
+          <t>2.87%→2.56%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -1888,11 +1888,11 @@
         <v>91</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>21541975</v>
+        <v>23514400</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>0.37%→0.44%</t>
+          <t>0.37%→0.43%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1909,11 +1909,11 @@
         <v>-101</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-55544950</v>
+        <v>-57777050</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.31%</t>
+          <t>0.45%→0.29%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -1932,11 +1932,11 @@
         <v>54</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>177174000</v>
+        <v>206550000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>1.87%→2.41%</t>
+          <t>1.98%→2.55%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1953,11 +1953,11 @@
         <v>-36</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-99450000</v>
+        <v>-110160000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>6.21%→5.89%</t>
+          <t>6.24%→5.91%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -1976,11 +1976,11 @@
         <v>16</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>47396000</v>
+        <v>54060000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>0.19%→0.34%</t>
+          <t>0.20%→0.35%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -1997,11 +1997,11 @@
         <v>-36</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-31518000</v>
+        <v>-33017400</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>0.19%→0.09%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2020,11 +2020,11 @@
         <v>15</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>32831250</v>
+        <v>39716250</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>0.56%→0.66%</t>
+          <t>0.61%→0.72%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2034,23 +2034,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>채비  (편출)</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-31501000</v>
+        <v>-17051000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.14%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>82→48</t>
+          <t>34→0</t>
         </is>
       </c>
     </row>
@@ -2064,11 +2064,11 @@
         <v>12</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>106998000</v>
+        <v>127500000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.32%→2.65%</t>
+          <t>2.51%→2.86%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2078,46 +2078,46 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>채비  (편출)</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-16010600</v>
+        <v>-30951900</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>0.21%→0.12%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>34→0</t>
+          <t>82→48</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>64515000</v>
+        <v>37740000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.81%→3.00%</t>
+          <t>1.20%→1.30%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>142→152</t>
+          <t>114→124</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
@@ -2129,7 +2129,7 @@
         <v>-31</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-46165200</v>
+        <v>-49985950</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2145,23 +2145,23 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>33405000</v>
+        <v>70805000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>1.17%→1.27%</t>
+          <t>2.80%→2.98%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>114→124</t>
+          <t>142→152</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -2173,11 +2173,11 @@
         <v>-27</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-77571000</v>
+        <v>-78259500</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.24%→0.00%</t>
+          <t>0.22%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2196,11 +2196,11 @@
         <v>9</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>17671500</v>
+        <v>18819000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.71%→2.76%</t>
+          <t>2.63%→2.67%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2210,23 +2210,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-35759500</v>
+        <v>-42423500</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.10%</t>
+          <t>0.70%→0.58%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
@@ -2240,11 +2240,11 @@
         <v>6</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>38709000</v>
+        <v>43350000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>0.91%→1.03%</t>
+          <t>0.93%→1.04%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2254,46 +2254,46 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-40162500</v>
+        <v>-37663500</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.61%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>27→13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>36618000</v>
+        <v>41616000</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.92%→1.03%</t>
+          <t>1.41%→1.52%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>49→55</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -2305,11 +2305,11 @@
         <v>-10</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-73610000</v>
+        <v>-71655000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.08%→0.86%</t>
+          <t>0.96%→0.76%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2321,23 +2321,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>38046000</v>
+        <v>39168000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>1.42%→1.53%</t>
+          <t>0.89%→1.00%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>49→55</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -2349,11 +2349,11 @@
         <v>-7</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-68544000</v>
+        <v>-81039000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>3.21%→2.99%</t>
+          <t>3.45%→3.21%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2372,11 +2372,11 @@
         <v>5</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>17722500</v>
+        <v>20123750</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>6.83%→6.87%</t>
+          <t>7.05%→7.08%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2393,11 +2393,11 @@
         <v>-6</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-18130500</v>
+        <v>-19176000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.73%</t>
+          <t>0.76%→0.70%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2416,11 +2416,11 @@
         <v>5</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>36337500</v>
+        <v>35275000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.11%</t>
+          <t>0.00%→0.10%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2437,11 +2437,11 @@
         <v>-3</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-73567500</v>
+        <v>-68722500</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.03%→1.80%</t>
+          <t>1.72%→1.52%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2460,11 +2460,11 @@
         <v>4</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>51748000</v>
+        <v>64396000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>2.50%→2.65%</t>
+          <t>2.82%→2.99%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 568억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 579억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B59" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260713.xlsx
+++ b/reports/pdf_rolling5_20260713.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,826억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 18종목  /  매도 15종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,826억   ·   현금 120억(2.4%)      오늘 2026-07-13  vs  5일전 2026-07-06      매수 18종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -751,18 +751,18 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>파두  (신규)</t>
+          <t>원익머트리얼즈  (신규)</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>66</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>5068800000</v>
+        <v>2484900000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.05%</t>
+          <t>0.00%→0.52%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -795,18 +795,18 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈  (신규)</t>
+          <t>파두  (신규)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>66</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2484900000</v>
+        <v>5068800000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.52%</t>
+          <t>0.00%→1.05%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -992,23 +992,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>RFHIC</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-17</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-885700000</v>
+        <v>-529550000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.88%→0.63%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>75→58</t>
+          <t>32→15</t>
         </is>
       </c>
     </row>
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>RFHIC</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-17</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-529550000</v>
+        <v>-885700000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>0.88%→0.63%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>32→15</t>
+          <t>75→58</t>
         </is>
       </c>
     </row>
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1597500000</v>
+        <v>1620000000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.69%→2.93%</t>
+          <t>3.60%→3.84%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G21" s="17" t="n"/>
@@ -1351,23 +1351,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1620000000</v>
+        <v>416500000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>3.60%→3.84%</t>
+          <t>2.65%→2.96%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>166→171</t>
         </is>
       </c>
       <c r="G22" s="17" t="n"/>
@@ -1379,23 +1379,23 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>416500000</v>
+        <v>1597500000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>2.65%→2.96%</t>
+          <t>2.69%→2.93%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G23" s="17" t="n"/>
@@ -1407,7 +1407,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,371억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,371억   ·   현금 38억(0.9%)      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1431,7 +1431,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,815억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,815억   ·   현금 53억(1.9%)      오늘 2026-07-13  vs  5일전 2026-07-06      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,598억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,598억   ·   현금 55억(2.1%)      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1748,7 +1748,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 363억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 15종목  /  매도 14종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 363억   ·   현금 5억(100.0%)      오늘 2026-07-13  vs  5일전 2026-07-06      매수 15종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1946,23 +1946,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-110160000</v>
+        <v>-33017400</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>6.24%→5.91%</t>
+          <t>0.19%→0.09%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>733→697</t>
+          <t>73→37</t>
         </is>
       </c>
     </row>
@@ -1990,23 +1990,23 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-33017400</v>
+        <v>-110160000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.19%→0.09%</t>
+          <t>6.24%→5.91%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>73→37</t>
+          <t>733→697</t>
         </is>
       </c>
     </row>
@@ -2034,23 +2034,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>채비  (편출)</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-17051000</v>
+        <v>-30951900</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>0.21%→0.12%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>34→0</t>
+          <t>82→48</t>
         </is>
       </c>
     </row>
@@ -2078,46 +2078,46 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>채비  (편출)</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-30951900</v>
+        <v>-17051000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.12%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>82→48</t>
+          <t>34→0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>37740000</v>
+        <v>70805000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>1.20%→1.30%</t>
+          <t>2.80%→2.98%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>114→124</t>
+          <t>142→152</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
@@ -2145,23 +2145,23 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>70805000</v>
+        <v>37740000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>2.80%→2.98%</t>
+          <t>1.20%→1.30%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>142→152</t>
+          <t>114→124</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -2233,23 +2233,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>43350000</v>
+        <v>39168000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>0.93%→1.04%</t>
+          <t>0.89%→1.00%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>46→52</t>
+          <t>49→55</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2321,23 +2321,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>39168000</v>
+        <v>43350000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>0.89%→1.00%</t>
+          <t>0.93%→1.04%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>49→55</t>
+          <t>46→52</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -2365,23 +2365,23 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>코스메카코리아  (신규)</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>20123750</v>
+        <v>35275000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>7.05%→7.08%</t>
+          <t>0.00%→0.10%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>629→634</t>
+          <t>0→5</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -2409,23 +2409,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>코스메카코리아  (신규)</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>35275000</v>
+        <v>20123750</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.10%</t>
+          <t>7.05%→7.08%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>0→5</t>
+          <t>629→634</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 579억      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 579억   ·   현금 18억(3.1%)      오늘 2026-07-13  vs  5일전 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B59" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260713.xlsx
+++ b/reports/pdf_rolling5_20260713.xlsx
@@ -751,18 +751,18 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈  (신규)</t>
+          <t>파두  (신규)</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>66</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2484900000</v>
+        <v>5068800000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.52%</t>
+          <t>0.00%→1.05%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -795,18 +795,18 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>파두  (신규)</t>
+          <t>원익머트리얼즈  (신규)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>66</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>5068800000</v>
+        <v>2484900000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.05%</t>
+          <t>0.00%→0.52%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -992,23 +992,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>RFHIC</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-17</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-529550000</v>
+        <v>-885700000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>0.88%→0.63%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>32→15</t>
+          <t>75→58</t>
         </is>
       </c>
     </row>
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>RFHIC</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-17</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-885700000</v>
+        <v>-529550000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.88%→0.63%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>75→58</t>
+          <t>32→15</t>
         </is>
       </c>
     </row>
@@ -1147,23 +1147,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>422000000</v>
+        <v>471500000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.23%→0.32%</t>
+          <t>1.82%→1.84%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>27→37</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>471500000</v>
+        <v>422000000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.82%→1.84%</t>
+          <t>0.23%→0.32%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>27→37</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1620000000</v>
+        <v>416500000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>3.60%→3.84%</t>
+          <t>2.65%→2.96%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>166→171</t>
         </is>
       </c>
       <c r="G21" s="17" t="n"/>
@@ -1351,23 +1351,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>416500000</v>
+        <v>1620000000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.65%→2.96%</t>
+          <t>3.60%→3.84%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G22" s="17" t="n"/>
@@ -1946,23 +1946,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-33017400</v>
+        <v>-110160000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.19%→0.09%</t>
+          <t>6.24%→5.91%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>73→37</t>
+          <t>733→697</t>
         </is>
       </c>
     </row>
@@ -1990,23 +1990,23 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-110160000</v>
+        <v>-33017400</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>6.24%→5.91%</t>
+          <t>0.19%→0.09%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>733→697</t>
+          <t>73→37</t>
         </is>
       </c>
     </row>
@@ -2210,23 +2210,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-42423500</v>
+        <v>-37663500</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.70%→0.58%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>27→13</t>
         </is>
       </c>
     </row>
@@ -2254,23 +2254,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-37663500</v>
+        <v>-42423500</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>0.70%→0.58%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
@@ -2365,23 +2365,23 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>코스메카코리아  (신규)</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>35275000</v>
+        <v>20123750</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.10%</t>
+          <t>7.05%→7.08%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>0→5</t>
+          <t>629→634</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -2409,23 +2409,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>코스메카코리아  (신규)</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>20123750</v>
+        <v>35275000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>7.05%→7.08%</t>
+          <t>0.00%→0.10%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>629→634</t>
+          <t>0→5</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260713.xlsx
+++ b/reports/pdf_rolling5_20260713.xlsx
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>416500000</v>
+        <v>1597500000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.65%→2.96%</t>
+          <t>2.69%→2.93%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G21" s="17" t="n"/>
@@ -1351,23 +1351,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1620000000</v>
+        <v>416500000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>3.60%→3.84%</t>
+          <t>2.65%→2.96%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>166→171</t>
         </is>
       </c>
       <c r="G22" s="17" t="n"/>
@@ -1379,23 +1379,23 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1597500000</v>
+        <v>1620000000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>2.69%→2.93%</t>
+          <t>3.60%→3.84%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G23" s="17" t="n"/>
@@ -2034,23 +2034,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>채비  (편출)</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-30951900</v>
+        <v>-17051000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.12%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>82→48</t>
+          <t>34→0</t>
         </is>
       </c>
     </row>
@@ -2078,46 +2078,46 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>채비  (편출)</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-17051000</v>
+        <v>-30951900</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>0.21%→0.12%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>34→0</t>
+          <t>82→48</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>70805000</v>
+        <v>37740000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.80%→2.98%</t>
+          <t>1.20%→1.30%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>142→152</t>
+          <t>114→124</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
@@ -2145,23 +2145,23 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>37740000</v>
+        <v>70805000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>1.20%→1.30%</t>
+          <t>2.80%→2.98%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>114→124</t>
+          <t>142→152</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -2210,90 +2210,90 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-37663500</v>
+        <v>-42423500</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>0.70%→0.58%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>39168000</v>
+        <v>41616000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>0.89%→1.00%</t>
+          <t>1.41%→1.52%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>49→55</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-42423500</v>
+        <v>-37663500</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.70%→0.58%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>27→13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>41616000</v>
+        <v>39168000</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>1.41%→1.52%</t>
+          <t>0.89%→1.00%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>49→55</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -2365,23 +2365,23 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>코스메카코리아  (신규)</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>20123750</v>
+        <v>35275000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>7.05%→7.08%</t>
+          <t>0.00%→0.10%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>629→634</t>
+          <t>0→5</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -2409,23 +2409,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>코스메카코리아  (신규)</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>35275000</v>
+        <v>20123750</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.10%</t>
+          <t>7.05%→7.08%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>0→5</t>
+          <t>629→634</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
